--- a/data/Тест по теме Взаимоотношения организмов (Биоинженеры) (Ответы).xlsx
+++ b/data/Тест по теме Взаимоотношения организмов (Биоинженеры) (Ответы).xlsx
@@ -1,17 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="22188" windowHeight="9324"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Ответы на форму (1)" sheetId="1" r:id="rId5"/>
+    <sheet name="Ответы на форму (1)" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="59">
   <si>
     <t>Отметка времени</t>
   </si>
@@ -176,100 +192,1017 @@
   </si>
   <si>
     <t>Для него возможен логистический рост численности, Для этого вида характерен положительный плотностно-зависимый эффект, При падении численности ниже определенной величины происходит необратимое падение численности, Для него будет характерен эффект Олли</t>
+  </si>
+  <si>
+    <t>st150414</t>
+  </si>
+  <si>
+    <t>Для него будет характерен эффект Олли</t>
+  </si>
+  <si>
+    <t>st097958</t>
+  </si>
+  <si>
+    <t>Для него будет характерен эффект Олли, Для него возможен экспоненциальный рост численности, Для него возможен логистический рост численности, При падении численности ниже определенной величины происходит необратимое падение численности, Для этого вида характерен положительный плотностно-зависимый эффект</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="0&quot; / 6&quot;"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="7">
+    <numFmt numFmtId="176" formatCode="_-* #\.##0.00_-;\-* #\.##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #\.##0.00\ &quot;₽&quot;_-;\-* #\.##0.00\ &quot;₽&quot;_-;_-* \-??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="m/d/yyyy\ h:mm:ss"/>
+    <numFmt numFmtId="181" formatCode="0&quot; / 6&quot;"/>
+    <numFmt numFmtId="182" formatCode="dd\.mm\.yyyy\ h:mm"/>
   </numFmts>
-  <fonts count="2">
-    <font>
-      <sz val="10.0"/>
+  <fonts count="23">
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F9FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F9FA"/>
+        <bgColor rgb="FFF8F9FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="16">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
+    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
+    <cellStyle name="Процент" xfId="3" builtinId="5"/>
+    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
+    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
+    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
+    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
+    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
+    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
+    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
+    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
+    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
+    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
+    <cellStyle name="Итого" xfId="21" builtinId="25"/>
+    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
+    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
+    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
+    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
+    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
+    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
+    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
+    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
+    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="13">
     <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
     </dxf>
     <dxf>
-      <font/>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF5B3F86"/>
           <bgColor rgb="FF5B3F86"/>
         </patternFill>
       </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-      <border/>
     </dxf>
     <dxf>
       <border>
@@ -289,43 +1222,40 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="4" pivot="0" name="Ответы на форму (1)-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="Ответы на форму (1)-style" pivot="0" count="4" xr9:uid="{4C4B00DE-AA7E-46DC-85BE-439AAC7611A0}">
+      <tableStyleElement type="wholeTable" dxfId="12"/>
+      <tableStyleElement type="headerRow" dxfId="11"/>
+      <tableStyleElement type="firstRowStripe" dxfId="10"/>
+      <tableStyleElement type="secondRowStripe" dxfId="9"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I12" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Form_Responses" displayName="Form_Responses" ref="A1:I12">
   <tableColumns count="9">
-    <tableColumn name="Отметка времени" id="1"/>
-    <tableColumn name="Баллы" id="2"/>
-    <tableColumn name="Найдите себя в списке" id="3"/>
-    <tableColumn name="Какой тип отношений наблюдается между устрицами и планктонными личинками полихет?" id="4"/>
-    <tableColumn name="Найдите животных, для которых характерен межвидовой гнездовой паразитизм" id="5"/>
-    <tableColumn name="Если для животного характерна групповая охота, что можно сказать относительно этого вида?" id="6"/>
-    <tableColumn name="Найдите среди приведенных ниже животных тех, которые склонны к клептопаразитизму" id="7"/>
-    <tableColumn name="Выделение во внешнюю среду токсинов, препятствующих росту численности конкурентов, является проявлением" id="8"/>
-    <tableColumn name="Поедание потомством тканей материнского организма является примером " id="9"/>
+    <tableColumn id="1" name="Отметка времени" dataDxfId="0"/>
+    <tableColumn id="2" name="Баллы" dataDxfId="1"/>
+    <tableColumn id="3" name="Найдите себя в списке" dataDxfId="2"/>
+    <tableColumn id="4" name="Какой тип отношений наблюдается между устрицами и планктонными личинками полихет?" dataDxfId="3"/>
+    <tableColumn id="5" name="Найдите животных, для которых характерен межвидовой гнездовой паразитизм" dataDxfId="4"/>
+    <tableColumn id="6" name="Если для животного характерна групповая охота, что можно сказать относительно этого вида?" dataDxfId="5"/>
+    <tableColumn id="7" name="Найдите среди приведенных ниже животных тех, которые склонны к клептопаразитизму" dataDxfId="6"/>
+    <tableColumn id="8" name="Выделение во внешнюю среду токсинов, препятствующих росту численности конкурентов, является проявлением" dataDxfId="7"/>
+    <tableColumn id="9" name="Поедание потомством тканей материнского организма является примером " dataDxfId="8"/>
   </tableColumns>
-  <tableStyleInfo name="Ответы на форму (1)-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Ответы на форму (1)-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -515,24 +1445,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:O14"/>
+  <sheetFormatPr defaultColWidth="12.6296296296296" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="19.0"/>
-    <col customWidth="1" min="2" max="2" width="18.88"/>
-    <col customWidth="1" min="3" max="3" width="22.88"/>
-    <col customWidth="1" min="4" max="9" width="37.63"/>
-    <col customWidth="1" min="10" max="15" width="18.88"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="18.8796296296296" customWidth="1"/>
+    <col min="3" max="3" width="22.8796296296296" customWidth="1"/>
+    <col min="4" max="9" width="37.6296296296296" customWidth="1"/>
+    <col min="10" max="15" width="18.8796296296296" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
+    <row r="1" ht="22.5" customHeight="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -561,12 +1493,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="22.5" customHeight="1">
+    <row r="2" ht="22.5" customHeight="1" spans="1:9">
       <c r="A2" s="2">
-        <v>46086.514862384254</v>
+        <v>46086.5148623843</v>
       </c>
       <c r="B2" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>9</v>
@@ -590,12 +1522,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" ht="22.5" customHeight="1">
+    <row r="3" ht="22.5" customHeight="1" spans="1:9">
       <c r="A3" s="2">
-        <v>46087.80667604167</v>
+        <v>46087.8066760417</v>
       </c>
       <c r="B3" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>16</v>
@@ -619,12 +1551,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" ht="22.5" customHeight="1">
+    <row r="4" ht="22.5" customHeight="1" spans="1:9">
       <c r="A4" s="2">
         <v>46087.8706827662</v>
       </c>
       <c r="B4" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>22</v>
@@ -648,12 +1580,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" ht="22.5" customHeight="1">
+    <row r="5" ht="22.5" customHeight="1" spans="1:9">
       <c r="A5" s="2">
-        <v>46087.91180050926</v>
+        <v>46087.9118005093</v>
       </c>
       <c r="B5" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>27</v>
@@ -677,12 +1609,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" ht="22.5" customHeight="1">
+    <row r="6" ht="22.5" customHeight="1" spans="1:9">
       <c r="A6" s="2">
-        <v>46087.91394327546</v>
+        <v>46087.9139432755</v>
       </c>
       <c r="B6" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>32</v>
@@ -706,12 +1638,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" ht="22.5" customHeight="1">
+    <row r="7" ht="22.5" customHeight="1" spans="1:9">
       <c r="A7" s="2">
-        <v>46087.91466277778</v>
+        <v>46087.9146627778</v>
       </c>
       <c r="B7" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>36</v>
@@ -735,12 +1667,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" ht="22.5" customHeight="1">
+    <row r="8" ht="22.5" customHeight="1" spans="1:9">
       <c r="A8" s="2">
-        <v>46087.942507604166</v>
+        <v>46087.9425076042</v>
       </c>
       <c r="B8" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>38</v>
@@ -764,12 +1696,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" ht="22.5" customHeight="1">
+    <row r="9" ht="22.5" customHeight="1" spans="1:9">
       <c r="A9" s="2">
-        <v>46087.944362361115</v>
+        <v>46087.9443623611</v>
       </c>
       <c r="B9" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>42</v>
@@ -793,12 +1725,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" ht="22.5" customHeight="1">
+    <row r="10" ht="22.5" customHeight="1" spans="1:9">
       <c r="A10" s="2">
-        <v>46087.96653951389</v>
+        <v>46087.9665395139</v>
       </c>
       <c r="B10" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>9</v>
@@ -822,12 +1754,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" ht="22.5" customHeight="1">
+    <row r="11" ht="22.5" customHeight="1" spans="1:9">
       <c r="A11" s="2">
-        <v>46087.97656594907</v>
+        <v>46087.9765659491</v>
       </c>
       <c r="B11" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>47</v>
@@ -851,12 +1783,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" ht="22.5" customHeight="1">
+    <row r="12" ht="22.5" customHeight="1" spans="1:9">
       <c r="A12" s="2">
-        <v>46087.982638807865</v>
+        <v>46087.9826388079</v>
       </c>
       <c r="B12" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>52</v>
@@ -880,10 +1812,81 @@
         <v>35</v>
       </c>
     </row>
+    <row r="13" customHeight="1" spans="1:15">
+      <c r="A13" s="5">
+        <v>46094.0994444444</v>
+      </c>
+      <c r="B13" s="3">
+        <v>3</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:15">
+      <c r="A14" s="7">
+        <v>46094.9853935185</v>
+      </c>
+      <c r="B14" s="8">
+        <v>5</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>